--- a/diseases/d153/2020-2025.xlsx
+++ b/diseases/d153/2020-2025.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>65</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>1.175489347173002</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>48</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.8680536717585249</v>
       </c>
@@ -2001,9 +1995,6 @@
       <c r="O9" t="n">
         <v>66</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>1.193573798667972</v>
       </c>
@@ -2545,9 +2536,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.9946448322233097</v>
       </c>
@@ -3089,9 +3077,6 @@
       <c r="O15" t="n">
         <v>45</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.813800317273617</v>
       </c>
@@ -3633,9 +3618,6 @@
       <c r="O18" t="n">
         <v>46</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.8318847687685863</v>
       </c>
@@ -4177,9 +4159,6 @@
       <c r="O21" t="n">
         <v>45</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.813800317273617</v>
       </c>
@@ -4721,9 +4700,6 @@
       <c r="O24" t="n">
         <v>62</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>1.121235992688095</v>
       </c>
@@ -5265,9 +5241,6 @@
       <c r="O27" t="n">
         <v>61</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>1.103151541193125</v>
       </c>
@@ -5809,9 +5782,6 @@
       <c r="O30" t="n">
         <v>68</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>1.22974270165791</v>
       </c>
@@ -6353,9 +6323,6 @@
       <c r="O33" t="n">
         <v>77</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>1.392502765112634</v>
       </c>
@@ -6897,9 +6864,6 @@
       <c r="O36" t="n">
         <v>45</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.813800317273617</v>
       </c>
@@ -7441,9 +7405,6 @@
       <c r="O39" t="n">
         <v>76</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>1.371575010264254</v>
       </c>
@@ -7985,9 +7946,6 @@
       <c r="O42" t="n">
         <v>61</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>1.100869416133151</v>
       </c>
@@ -8529,9 +8487,6 @@
       <c r="O45" t="n">
         <v>66</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>1.191104614176852</v>
       </c>
@@ -9073,9 +9028,6 @@
       <c r="O48" t="n">
         <v>67</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>1.209151653785592</v>
       </c>
@@ -9617,9 +9569,6 @@
       <c r="O51" t="n">
         <v>79</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>1.425716129090474</v>
       </c>
@@ -10161,9 +10110,6 @@
       <c r="O54" t="n">
         <v>67</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>1.209151653785592</v>
       </c>
@@ -10705,9 +10651,6 @@
       <c r="O57" t="n">
         <v>55</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.99258717848071</v>
       </c>
@@ -11249,9 +11192,6 @@
       <c r="O60" t="n">
         <v>80</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>1.443763168699215</v>
       </c>
@@ -11793,9 +11733,6 @@
       <c r="O63" t="n">
         <v>65</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>1.173057574568112</v>
       </c>
@@ -12337,9 +12274,6 @@
       <c r="O66" t="n">
         <v>67</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>1.209151653785592</v>
       </c>
@@ -12881,9 +12815,6 @@
       <c r="O69" t="n">
         <v>95</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>1.714468762830317</v>
       </c>
@@ -13425,9 +13356,6 @@
       <c r="O72" t="n">
         <v>79</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>1.425716129090474</v>
       </c>
@@ -13969,9 +13897,6 @@
       <c r="O75" t="n">
         <v>63</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>1.131201610831094</v>
       </c>
@@ -14513,9 +14438,6 @@
       <c r="O78" t="n">
         <v>54</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.969601380712366</v>
       </c>
@@ -15057,9 +14979,6 @@
       <c r="O81" t="n">
         <v>94</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>1.687824625684489</v>
       </c>
@@ -15601,9 +15520,6 @@
       <c r="O84" t="n">
         <v>71</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>1.274846259825518</v>
       </c>
@@ -16145,9 +16061,6 @@
       <c r="O87" t="n">
         <v>96</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>1.723735787933095</v>
       </c>
@@ -16689,9 +16602,6 @@
       <c r="O90" t="n">
         <v>65</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>1.1671127730797</v>
       </c>
@@ -17233,9 +17143,6 @@
       <c r="O93" t="n">
         <v>68</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>1.220979516452609</v>
       </c>
@@ -17777,9 +17684,6 @@
       <c r="O96" t="n">
         <v>72</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>1.292801840949822</v>
       </c>
@@ -18321,9 +18225,6 @@
       <c r="O99" t="n">
         <v>78</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>1.40053532769564</v>
       </c>
@@ -18865,9 +18766,6 @@
       <c r="O102" t="n">
         <v>96</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>1.723735787933095</v>
       </c>
@@ -19409,9 +19307,6 @@
       <c r="O105" t="n">
         <v>84</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>1.508268814441458</v>
       </c>
@@ -19953,9 +19848,6 @@
       <c r="O108" t="n">
         <v>78</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>1.40053532769564</v>
       </c>
@@ -20497,9 +20389,6 @@
       <c r="O111" t="n">
         <v>54</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.9640816216495597</v>
       </c>
@@ -21041,9 +20930,6 @@
       <c r="O114" t="n">
         <v>69</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>1.231882072107771</v>
       </c>
@@ -21585,9 +21471,6 @@
       <c r="O117" t="n">
         <v>83</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>1.481829159202101</v>
       </c>
@@ -22129,9 +22012,6 @@
       <c r="O120" t="n">
         <v>70</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>1.249735435471651</v>
       </c>
@@ -22673,9 +22553,6 @@
       <c r="O123" t="n">
         <v>74</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>1.321148888927174</v>
       </c>
@@ -23217,9 +23094,6 @@
       <c r="O126" t="n">
         <v>89</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>1.588949339385386</v>
       </c>
@@ -23761,9 +23635,6 @@
       <c r="O129" t="n">
         <v>73</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>1.303295525563294</v>
       </c>
@@ -24305,9 +24176,6 @@
       <c r="O132" t="n">
         <v>70</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>1.249735435471651</v>
       </c>
@@ -24849,9 +24717,6 @@
       <c r="O135" t="n">
         <v>83</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>1.481829159202101</v>
       </c>
@@ -25393,9 +25258,6 @@
       <c r="O138" t="n">
         <v>67</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>1.196175345380009</v>
       </c>
@@ -25937,9 +25799,6 @@
       <c r="O141" t="n">
         <v>58</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>1.035495075105083</v>
       </c>
@@ -26481,9 +26340,6 @@
       <c r="O144" t="n">
         <v>58</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>1.035495075105083</v>
       </c>
@@ -27025,9 +26881,6 @@
       <c r="O147" t="n">
         <v>68</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>1.210543729067496</v>
       </c>
@@ -27569,9 +27422,6 @@
       <c r="O150" t="n">
         <v>59</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>1.05032470610268</v>
       </c>
@@ -28113,9 +27963,6 @@
       <c r="O153" t="n">
         <v>69</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>1.228345842730253</v>
       </c>
@@ -28657,9 +28504,6 @@
       <c r="O156" t="n">
         <v>63</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>1.121533160753709</v>
       </c>
@@ -29201,9 +29045,6 @@
       <c r="O159" t="n">
         <v>78</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>1.388564865695069</v>
       </c>
@@ -29745,9 +29586,6 @@
       <c r="O162" t="n">
         <v>67</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>1.192741615404739</v>
       </c>
@@ -30289,9 +30127,6 @@
       <c r="O165" t="n">
         <v>45</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.8010951148240782</v>
       </c>
@@ -30833,9 +30668,6 @@
       <c r="O168" t="n">
         <v>67</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>1.192741615404739</v>
       </c>
@@ -31377,9 +31209,6 @@
       <c r="O171" t="n">
         <v>80</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>1.424169093020583</v>
       </c>
@@ -31921,9 +31750,6 @@
       <c r="O174" t="n">
         <v>63</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>1.121533160753709</v>
       </c>
@@ -32465,9 +32291,6 @@
       <c r="O177" t="n">
         <v>74</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>1.31735641104404</v>
       </c>
@@ -33009,9 +32832,6 @@
       <c r="O180" t="n">
         <v>54</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.9613141377888939</v>
       </c>
@@ -33553,9 +33373,6 @@
       <c r="O183" t="n">
         <v>82</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>1.458210833990788</v>
       </c>
@@ -34097,9 +33914,6 @@
       <c r="O186" t="n">
         <v>59</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>1.049200478115323</v>
       </c>
@@ -34641,9 +34455,6 @@
       <c r="O189" t="n">
         <v>69</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>1.227031067626395</v>
       </c>
@@ -35185,9 +34996,6 @@
       <c r="O192" t="n">
         <v>75</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>1.333729421333038</v>
       </c>
@@ -35729,9 +35537,6 @@
       <c r="O195" t="n">
         <v>71</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>1.262597185528609</v>
       </c>
@@ -36273,9 +36078,6 @@
       <c r="O198" t="n">
         <v>63</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>1.120332713919752</v>
       </c>
@@ -36817,9 +36619,6 @@
       <c r="O201" t="n">
         <v>68</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>1.209248008675287</v>
       </c>
@@ -37361,9 +37160,6 @@
       <c r="O204" t="n">
         <v>72</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>1.280380244479716</v>
       </c>
@@ -37905,9 +37701,6 @@
       <c r="O207" t="n">
         <v>76</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>1.351512480284145</v>
       </c>
@@ -38449,9 +38242,6 @@
       <c r="O210" t="n">
         <v>79</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>1.404861657137466</v>
       </c>
@@ -38993,9 +38783,6 @@
       <c r="O213" t="n">
         <v>64</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>1.138115772870859</v>
       </c>
@@ -39536,9 +39323,6 @@
       </c>
       <c r="O216" t="n">
         <v>51</v>
-      </c>
-      <c r="Q216" t="n">
-        <v>0</v>
       </c>
       <c r="R216" t="n">
         <v>0.9069360065064657</v>
